--- a/it_forms/013_virus_removal_analysis_form--it_forms.xlsx
+++ b/it_forms/013_virus_removal_analysis_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,8 +1083,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'it_technician'}</t>
+          <t>it_technician</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'IT Technician'}</t>
+          <t>IT Technician</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'repair_shop'}</t>
+          <t>repair_shop</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Repair Shop'}</t>
+          <t>Repair Shop</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'it_department'}</t>
+          <t>it_department</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'IT Department'}</t>
+          <t>IT Department</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'help_desk'}</t>
+          <t>help_desk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Help Desk'}</t>
+          <t>Help Desk</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'it_technician'}</t>
+          <t>it_technician</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'IT Technician'}</t>
+          <t>IT Technician</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'repair_shop'}</t>
+          <t>repair_shop</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Repair Shop'}</t>
+          <t>Repair Shop</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'virus_removal'}</t>
+          <t>virus_removal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Virus Removal'}</t>
+          <t>Virus Removal</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'data_recovery'}</t>
+          <t>data_recovery</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Data Recovery'}</t>
+          <t>Data Recovery</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'virus'}</t>
+          <t>virus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'virus'}</t>
+          <t>virus</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
